--- a/funcionarios.xlsx
+++ b/funcionarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,427 +448,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gerente</t>
+          <t>Diretor</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dsds</t>
+          <t>Vinicius</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dsds</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>dsd</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Vini</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Vini</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vini</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Vini</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SDS</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DSDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SDS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DSDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SDS</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DSDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SDS</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DSDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>DSDS</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SDSD</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SDSD</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SDSD</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Vini</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dsd</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Supessrvisor</t>
+          <t>aa</t>
         </is>
       </c>
     </row>

--- a/funcionarios.xlsx
+++ b/funcionarios.xlsx
@@ -2,28 +2,36 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Funcionários" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ocorrências" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Relatórios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,12 +45,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -55,14 +78,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,38 +453,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nome: </t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Função: </t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dias afastados: </t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">teve danos: </t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tipo de acidente: </t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data ocorrência: </t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>cargo</t>
         </is>
       </c>
     </row>
@@ -468,24 +476,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gerente</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Acidente</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1005</v>
+          <t>Supervisor</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -496,26 +488,795 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Supessrvisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kleber</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Gerente</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Matheus</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Paulo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Operário</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lindao</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>cargo</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Dias afastados</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Lesão</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Incidente</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Incidente</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quase Acidente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Acidente</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quase Acidente</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Incidente</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Lindao</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Acidente</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Incidente</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Acidente</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Acidente</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gerente</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Acidente</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Mês</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Efetivo</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Hht</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Total Acidentes</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Dias afastados</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>TG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fevereiro</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>223</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>223</v>
+      </c>
+      <c r="C3" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>223</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Julho</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>223</v>
+      </c>
+      <c r="C5" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>223</v>
+      </c>
+      <c r="C6" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>61.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Setembro</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>223</v>
+      </c>
+      <c r="C7" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Outubro</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>223</v>
+      </c>
+      <c r="C8" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Março</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>223</v>
+      </c>
+      <c r="C9" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Novembro</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>223</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>224.22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>223</v>
+      </c>
+      <c r="C11" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dezembro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>223</v>
+      </c>
+      <c r="C12" t="n">
+        <v>49060</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="G12" t="n">
+        <v>101.92</v>
       </c>
     </row>
   </sheetData>
